--- a/XLibur.Tests/Resource/Examples/Misc/Collections.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Collections.xlsx
@@ -21,67 +21,67 @@
     <x:t>Strings</x:t>
   </x:si>
   <x:si>
+    <x:t>House</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Car</x:t>
+  </x:si>
+  <x:si>
     <x:t>Arrays</x:t>
   </x:si>
   <x:si>
-    <x:t>House</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Car</x:t>
-  </x:si>
-  <x:si>
     <x:t>DataTable</x:t>
   </x:si>
   <x:si>
+    <x:t>Indocin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>David</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Enebrel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sam</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hydralazine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Christoff</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Combivent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Janet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dilantin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Melanie</x:t>
+  </x:si>
+  <x:si>
     <x:t>Query</x:t>
   </x:si>
   <x:si>
-    <x:t>Indocin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>David</x:t>
-  </x:si>
-  <x:si>
     <x:t>John</x:t>
   </x:si>
   <x:si>
     <x:t>On Elm St.</x:t>
   </x:si>
   <x:si>
-    <x:t>Enebrel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sam</x:t>
-  </x:si>
-  <x:si>
     <x:t>Luis</x:t>
   </x:si>
   <x:si>
     <x:t>On 23rd St.</x:t>
   </x:si>
   <x:si>
-    <x:t>Hydralazine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Christoff</x:t>
-  </x:si>
-  <x:si>
     <x:t>Henry</x:t>
   </x:si>
   <x:si>
     <x:t>On 5th Ave.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Combivent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Janet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dilantin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Melanie</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -477,7 +477,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="1"/>
@@ -487,7 +487,7 @@
     </x:row>
     <x:row r="2" spans="1:8">
       <x:c r="A2" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>1</x:v>
@@ -501,7 +501,7 @@
     </x:row>
     <x:row r="3" spans="1:8">
       <x:c r="A3" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>1</x:v>
@@ -535,7 +535,7 @@
       <x:c r="C6" s="1"/>
       <x:c r="D6" s="1"/>
       <x:c r="F6" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="1"/>
       <x:c r="H6" s="1"/>
@@ -545,19 +545,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="2">
         <x:v>36526</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>30</x:v>
@@ -568,19 +568,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D8" s="2">
         <x:v>36527</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="0">
         <x:v>21</x:v>
@@ -591,19 +591,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="2">
         <x:v>36528</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>45</x:v>
@@ -614,10 +614,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D10" s="2">
         <x:v>36529</x:v>
@@ -628,10 +628,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D11" s="2">
         <x:v>36530</x:v>

--- a/XLibur.Tests/Resource/Examples/Misc/Collections.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Collections.xlsx
@@ -456,20 +456,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:H11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="7.282054" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="1.853482" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="6.139196" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="3.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="7.282054" customWidth="1"/>
+    <x:col min="2" max="2" width="11.424911" customWidth="1"/>
+    <x:col min="3" max="3" width="8.710625" customWidth="1"/>
+    <x:col min="4" max="4" width="9.282054" customWidth="1"/>
+    <x:col min="5" max="5" width="1.853482" customWidth="1"/>
+    <x:col min="6" max="6" width="6.139196" customWidth="1"/>
+    <x:col min="7" max="7" width="11.424911" customWidth="1"/>
+    <x:col min="8" max="8" width="3.139196" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
@@ -486,44 +483,44 @@
       <x:c r="H1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:8">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="0">
+      <x:c r="C2">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D2" s="0">
+      <x:c r="D2">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E2" s="0">
+      <x:c r="E2">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
-      <x:c r="C4" s="0">
+      <x:c r="C4">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D4" s="0">
+      <x:c r="D4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E4" s="0">
+      <x:c r="E4">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F4" s="0">
+      <x:c r="F4">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G4" s="0">
+      <x:c r="G4">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H4" s="0">
+      <x:c r="H4">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -541,82 +538,82 @@
       <x:c r="H6" s="1"/>
     </x:row>
     <x:row r="7" spans="1:8">
-      <x:c r="A7" s="0">
+      <x:c r="A7">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="B7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="C7" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D7" s="2">
         <x:v>36526</x:v>
       </x:c>
-      <x:c r="F7" s="0" t="s">
+      <x:c r="F7" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
+      <x:c r="G7" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H7" s="0">
+      <x:c r="H7">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="A8" s="0">
+      <x:c r="A8">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="B8" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
+      <x:c r="C8" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D8" s="2">
         <x:v>36527</x:v>
       </x:c>
-      <x:c r="F8" s="0" t="s">
+      <x:c r="F8" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
+      <x:c r="G8" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="0">
+      <x:c r="H8">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:8">
-      <x:c r="A9" s="0">
+      <x:c r="A9">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="B9" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
+      <x:c r="C9" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="2">
         <x:v>36528</x:v>
       </x:c>
-      <x:c r="F9" s="0" t="s">
+      <x:c r="F9" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G9" s="0" t="s">
+      <x:c r="G9" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="H9" s="0">
+      <x:c r="H9">
         <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
-      <x:c r="A10" s="0">
+      <x:c r="A10">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
+      <x:c r="B10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C10" s="0" t="s">
+      <x:c r="C10" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D10" s="2">
@@ -624,13 +621,13 @@
       </x:c>
     </x:row>
     <x:row r="11" spans="1:8">
-      <x:c r="A11" s="0">
+      <x:c r="A11">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
+      <x:c r="B11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="0" t="s">
+      <x:c r="C11" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D11" s="2">
@@ -643,10 +640,6 @@
     <x:mergeCell ref="A6:D6"/>
     <x:mergeCell ref="F6:H6"/>
   </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Misc/Collections.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Collections.xlsx
@@ -459,13 +459,13 @@
   <x:dimension ref="A1:H11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="7.282054" customWidth="1"/>
-    <x:col min="2" max="2" width="11.424911" customWidth="1"/>
-    <x:col min="3" max="3" width="8.710625" customWidth="1"/>
-    <x:col min="4" max="4" width="9.282054" customWidth="1"/>
-    <x:col min="5" max="5" width="1.853482" customWidth="1"/>
+    <x:col min="1" max="1" width="6.996339" customWidth="1"/>
+    <x:col min="2" max="2" width="11.139196" customWidth="1"/>
+    <x:col min="3" max="3" width="8.424911" customWidth="1"/>
+    <x:col min="4" max="4" width="8.996339" customWidth="1"/>
+    <x:col min="5" max="5" width="2.139196" customWidth="1"/>
     <x:col min="6" max="6" width="6.139196" customWidth="1"/>
-    <x:col min="7" max="7" width="11.424911" customWidth="1"/>
+    <x:col min="7" max="7" width="11.139196" customWidth="1"/>
     <x:col min="8" max="8" width="3.139196" customWidth="1"/>
   </x:cols>
   <x:sheetData>

--- a/XLibur.Tests/Resource/Examples/Misc/Collections.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Collections.xlsx
@@ -459,14 +459,14 @@
   <x:dimension ref="A1:H11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="6.996339" customWidth="1"/>
-    <x:col min="2" max="2" width="11.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="8.424911" customWidth="1"/>
-    <x:col min="4" max="4" width="8.996339" customWidth="1"/>
-    <x:col min="5" max="5" width="2.139196" customWidth="1"/>
-    <x:col min="6" max="6" width="6.139196" customWidth="1"/>
-    <x:col min="7" max="7" width="11.139196" customWidth="1"/>
-    <x:col min="8" max="8" width="3.139196" customWidth="1"/>
+    <x:col min="1" max="1" width="7" customWidth="1"/>
+    <x:col min="2" max="2" width="11.142857" customWidth="1"/>
+    <x:col min="3" max="3" width="8.428571" customWidth="1"/>
+    <x:col min="4" max="4" width="9" customWidth="1"/>
+    <x:col min="5" max="5" width="2.142857" customWidth="1"/>
+    <x:col min="6" max="6" width="6.142857" customWidth="1"/>
+    <x:col min="7" max="7" width="11.142857" customWidth="1"/>
+    <x:col min="8" max="8" width="3.142857" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
